--- a/config/Flipkart_dropdown.xlsx
+++ b/config/Flipkart_dropdown.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D0968F-804B-4C36-A7A3-C9FFC2566FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452FE074-9917-49DA-B262-B7E3C6FAECF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="1" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
   <sheets>
     <sheet name="ActualColorDropdown-Tshirts" sheetId="5" r:id="rId1"/>
-    <sheet name="ActualColorDropdown-KidsTshirts" sheetId="6" r:id="rId2"/>
+    <sheet name="Dropdown-Kids T-shirt" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ActualColorDropdown-KidsTshirts'!$A$1:$E$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ActualColorDropdown-Tshirts'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dropdown-Kids T-shirt'!$A$1:$D$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="111">
   <si>
     <t>Blue</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>Short Sleeve</t>
+  </si>
+  <si>
+    <t>Kids T-shirt</t>
   </si>
 </sst>
 </file>
@@ -1442,13 +1445,13 @@
         <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
         <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1456,13 +1459,13 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
         <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -1470,13 +1473,13 @@
         <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -1484,13 +1487,13 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -1498,13 +1501,13 @@
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -1512,13 +1515,13 @@
         <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -1526,13 +1529,13 @@
         <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -1540,13 +1543,13 @@
         <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -1554,13 +1557,13 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
         <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -1568,13 +1571,13 @@
         <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
         <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1588,7 +1591,7 @@
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -1602,7 +1605,7 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -1616,7 +1619,7 @@
         <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -1630,7 +1633,7 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -1644,7 +1647,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -1658,7 +1661,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1672,7 +1675,7 @@
         <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1680,13 +1683,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -1700,7 +1703,7 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1714,7 +1717,7 @@
         <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1728,7 +1731,7 @@
         <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1736,13 +1739,13 @@
         <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
         <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -1756,7 +1759,7 @@
         <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1770,7 +1773,7 @@
         <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1784,7 +1787,7 @@
         <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1798,7 +1801,7 @@
         <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -1812,7 +1815,7 @@
         <v>98</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1826,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -1840,7 +1843,7 @@
         <v>102</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -1854,7 +1857,7 @@
         <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -1868,7 +1871,7 @@
         <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -1882,7 +1885,7 @@
         <v>108</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -1896,7 +1899,7 @@
         <v>87</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -1910,7 +1913,7 @@
         <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -1924,7 +1927,7 @@
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -1938,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -1952,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -1966,7 +1969,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
@@ -1980,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -1994,7 +1997,7 @@
         <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -2008,7 +2011,7 @@
         <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -2016,13 +2019,13 @@
         <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
@@ -2030,13 +2033,13 @@
         <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -2044,13 +2047,13 @@
         <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C45" t="s">
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -2064,7 +2067,7 @@
         <v>72</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -2078,7 +2081,7 @@
         <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -2086,13 +2089,13 @@
         <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -2106,7 +2109,7 @@
         <v>83</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -2120,7 +2123,7 @@
         <v>77</v>
       </c>
       <c r="D50" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -2134,7 +2137,7 @@
         <v>84</v>
       </c>
       <c r="D51" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -2148,7 +2151,7 @@
         <v>85</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -2162,7 +2165,7 @@
         <v>80</v>
       </c>
       <c r="D53" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -2176,7 +2179,7 @@
         <v>82</v>
       </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/config/Flipkart_dropdown.xlsx
+++ b/config/Flipkart_dropdown.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452FE074-9917-49DA-B262-B7E3C6FAECF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3553460C-AF4C-4E12-B176-E58A7CFBF320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="1" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
   <sheets>
-    <sheet name="ActualColorDropdown-Tshirts" sheetId="5" r:id="rId1"/>
-    <sheet name="Dropdown-Kids T-shirt" sheetId="6" r:id="rId2"/>
+    <sheet name="Dropdown-Tshirts" sheetId="5" r:id="rId1"/>
+    <sheet name="Dropdown-Kids Tshirts" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ActualColorDropdown-Tshirts'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dropdown-Kids T-shirt'!$A$1:$D$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dropdown-Kids Tshirts'!$A$1:$D$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dropdown-Tshirts'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="110">
   <si>
     <t>Blue</t>
   </si>
@@ -371,9 +371,6 @@
   </si>
   <si>
     <t>Short Sleeve</t>
-  </si>
-  <si>
-    <t>Kids T-shirt</t>
   </si>
 </sst>
 </file>
@@ -1445,13 +1442,13 @@
         <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
         <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1459,13 +1456,13 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
         <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -1473,13 +1470,13 @@
         <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -1487,13 +1484,13 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -1501,13 +1498,13 @@
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -1515,13 +1512,13 @@
         <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -1529,13 +1526,13 @@
         <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -1543,13 +1540,13 @@
         <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -1557,13 +1554,13 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
         <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -1571,13 +1568,13 @@
         <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
         <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1591,7 +1588,7 @@
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -1605,7 +1602,7 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -1619,7 +1616,7 @@
         <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -1633,7 +1630,7 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -1647,7 +1644,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -1661,7 +1658,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1675,7 +1672,7 @@
         <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1683,13 +1680,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -1703,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1717,7 +1714,7 @@
         <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1731,7 +1728,7 @@
         <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1739,13 +1736,13 @@
         <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
         <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -1759,7 +1756,7 @@
         <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1773,7 +1770,7 @@
         <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1787,7 +1784,7 @@
         <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1801,7 +1798,7 @@
         <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -1815,7 +1812,7 @@
         <v>98</v>
       </c>
       <c r="D28" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1829,7 +1826,7 @@
         <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -1843,7 +1840,7 @@
         <v>102</v>
       </c>
       <c r="D30" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -1857,7 +1854,7 @@
         <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -1871,7 +1868,7 @@
         <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -1885,7 +1882,7 @@
         <v>108</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -1899,7 +1896,7 @@
         <v>87</v>
       </c>
       <c r="D34" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -1913,7 +1910,7 @@
         <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -1927,7 +1924,7 @@
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -1941,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -1955,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -1969,7 +1966,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
@@ -1983,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -1997,7 +1994,7 @@
         <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -2011,7 +2008,7 @@
         <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -2019,13 +2016,13 @@
         <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
@@ -2033,13 +2030,13 @@
         <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -2047,13 +2044,13 @@
         <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C45" t="s">
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -2067,7 +2064,7 @@
         <v>72</v>
       </c>
       <c r="D46" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -2081,7 +2078,7 @@
         <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -2089,13 +2086,13 @@
         <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -2109,7 +2106,7 @@
         <v>83</v>
       </c>
       <c r="D49" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -2123,7 +2120,7 @@
         <v>77</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -2137,7 +2134,7 @@
         <v>84</v>
       </c>
       <c r="D51" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -2151,7 +2148,7 @@
         <v>85</v>
       </c>
       <c r="D52" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -2165,7 +2162,7 @@
         <v>80</v>
       </c>
       <c r="D53" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -2179,7 +2176,7 @@
         <v>82</v>
       </c>
       <c r="D54" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/config/Flipkart_dropdown.xlsx
+++ b/config/Flipkart_dropdown.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3553460C-AF4C-4E12-B176-E58A7CFBF320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680B80BA-532F-4E10-A5B5-72FD8CEEC32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="1" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Dropdown-Kids Tshirts" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dropdown-Kids Tshirts'!$A$1:$D$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dropdown-Kids Tshirts'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dropdown-Tshirts'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="111">
   <si>
     <t>Blue</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>Short Sleeve</t>
+  </si>
+  <si>
+    <t>Kids Tshirts</t>
   </si>
 </sst>
 </file>
@@ -1420,7 +1423,8 @@
   <cols>
     <col min="1" max="1" width="27.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -1442,13 +1446,13 @@
         <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
         <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1456,13 +1460,13 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
         <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -1470,13 +1474,13 @@
         <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -1484,13 +1488,13 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -1498,13 +1502,13 @@
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -1512,13 +1516,13 @@
         <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -1526,13 +1530,13 @@
         <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -1540,13 +1544,13 @@
         <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -1554,13 +1558,13 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
         <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -1568,13 +1572,13 @@
         <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
         <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1588,7 +1592,7 @@
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -1602,7 +1606,7 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -1616,7 +1620,7 @@
         <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -1630,7 +1634,7 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -1644,7 +1648,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -1658,7 +1662,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1672,7 +1676,7 @@
         <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1680,13 +1684,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -1700,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1714,7 +1718,7 @@
         <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1728,7 +1732,7 @@
         <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1736,13 +1740,13 @@
         <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
         <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -1756,7 +1760,7 @@
         <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1770,7 +1774,7 @@
         <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1784,7 +1788,7 @@
         <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1798,7 +1802,7 @@
         <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -1812,7 +1816,7 @@
         <v>98</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1826,7 +1830,7 @@
         <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -1840,7 +1844,7 @@
         <v>102</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -1854,7 +1858,7 @@
         <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -1868,7 +1872,7 @@
         <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -1882,7 +1886,7 @@
         <v>108</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -1896,7 +1900,7 @@
         <v>87</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -1910,7 +1914,7 @@
         <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -1924,7 +1928,7 @@
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -1938,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -1952,7 +1956,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -1966,7 +1970,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
@@ -1980,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -1994,7 +1998,7 @@
         <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -2008,7 +2012,7 @@
         <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -2016,13 +2020,13 @@
         <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
@@ -2030,13 +2034,13 @@
         <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -2044,13 +2048,13 @@
         <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C45" t="s">
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -2064,7 +2068,7 @@
         <v>72</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -2078,7 +2082,7 @@
         <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -2086,13 +2090,13 @@
         <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -2106,7 +2110,7 @@
         <v>83</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -2120,7 +2124,7 @@
         <v>77</v>
       </c>
       <c r="D50" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -2134,7 +2138,7 @@
         <v>84</v>
       </c>
       <c r="D51" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -2148,7 +2152,7 @@
         <v>85</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -2162,7 +2166,7 @@
         <v>80</v>
       </c>
       <c r="D53" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -2176,7 +2180,7 @@
         <v>82</v>
       </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/config/Flipkart_dropdown.xlsx
+++ b/config/Flipkart_dropdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680B80BA-532F-4E10-A5B5-72FD8CEEC32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D656898E-4067-40E7-91FF-AFE9004A9C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="1" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="112">
   <si>
     <t>Blue</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>Kids Tshirts</t>
+  </si>
+  <si>
+    <t>Flipkart Category</t>
   </si>
 </sst>
 </file>
@@ -1438,7 +1441,7 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">

--- a/config/Flipkart_dropdown.xlsx
+++ b/config/Flipkart_dropdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D656898E-4067-40E7-91FF-AFE9004A9C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4143ED80-519E-404F-ACAB-8555D3108B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="1" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="116">
   <si>
     <t>Blue</t>
   </si>
@@ -377,6 +377,18 @@
   </si>
   <si>
     <t>Flipkart Category</t>
+  </si>
+  <si>
+    <t>Boys</t>
+  </si>
+  <si>
+    <t>Girls</t>
+  </si>
+  <si>
+    <t>60% Cotton 40% Polyester</t>
+  </si>
+  <si>
+    <t>Cotton Blend</t>
   </si>
 </sst>
 </file>
@@ -1421,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B24816C5-4C62-46C4-A958-7B4B4D77D485}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.453125" bestFit="1" customWidth="1"/>
@@ -1642,13 +1654,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
         <v>110</v>
@@ -1659,10 +1671,10 @@
         <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
         <v>110</v>
@@ -1670,13 +1682,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
         <v>110</v>
@@ -1684,13 +1696,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" t="s">
-        <v>14</v>
+        <v>112</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="D19" t="s">
         <v>110</v>
@@ -1698,13 +1710,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" s="3">
-        <v>1</v>
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="D20" t="s">
         <v>110</v>
@@ -1712,13 +1724,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
         <v>110</v>
@@ -1726,13 +1738,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>26</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
         <v>110</v>
@@ -1740,13 +1752,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
         <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
         <v>110</v>
@@ -1754,13 +1766,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
+        <v>61</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
       </c>
       <c r="D24" t="s">
         <v>110</v>
@@ -1768,13 +1780,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" t="s">
-        <v>92</v>
+        <v>43</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="D25" t="s">
         <v>110</v>
@@ -1782,13 +1794,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
-      </c>
-      <c r="C26" t="s">
-        <v>94</v>
+        <v>63</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="D26" t="s">
         <v>110</v>
@@ -1796,13 +1808,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" t="s">
-        <v>96</v>
+        <v>30</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D27" t="s">
         <v>110</v>
@@ -1810,13 +1822,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" t="s">
-        <v>98</v>
+        <v>26</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D28" t="s">
         <v>110</v>
@@ -1824,13 +1836,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s">
         <v>110</v>
@@ -1841,10 +1853,10 @@
         <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
         <v>110</v>
@@ -1855,10 +1867,10 @@
         <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
         <v>110</v>
@@ -1869,10 +1881,10 @@
         <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
         <v>110</v>
@@ -1883,10 +1895,10 @@
         <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
         <v>110</v>
@@ -1894,13 +1906,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
         <v>110</v>
@@ -1908,13 +1920,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D35" t="s">
         <v>110</v>
@@ -1922,13 +1934,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B36" t="s">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
         <v>110</v>
@@ -1936,13 +1948,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B37" t="s">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="D37" t="s">
         <v>110</v>
@@ -1950,13 +1962,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B38" t="s">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
         <v>110</v>
@@ -1964,13 +1976,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="D39" t="s">
         <v>110</v>
@@ -1981,10 +1993,10 @@
         <v>75</v>
       </c>
       <c r="B40" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>0</v>
+        <v>87</v>
+      </c>
+      <c r="C40" t="s">
+        <v>87</v>
       </c>
       <c r="D40" t="s">
         <v>110</v>
@@ -1992,13 +2004,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>42</v>
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
+        <v>88</v>
       </c>
       <c r="D41" t="s">
         <v>110</v>
@@ -2006,13 +2018,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>42</v>
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2</v>
       </c>
       <c r="D42" t="s">
         <v>110</v>
@@ -2020,13 +2032,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="C43" t="s">
+        <v>0</v>
       </c>
       <c r="D43" t="s">
         <v>110</v>
@@ -2034,13 +2046,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1</v>
       </c>
       <c r="D44" t="s">
         <v>110</v>
@@ -2048,13 +2060,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="D45" t="s">
         <v>110</v>
@@ -2062,13 +2074,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
-      </c>
-      <c r="C46" t="s">
-        <v>72</v>
+        <v>3</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="D46" t="s">
         <v>110</v>
@@ -2076,13 +2088,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
-      </c>
-      <c r="C47" t="s">
-        <v>27</v>
+        <v>41</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D47" t="s">
         <v>110</v>
@@ -2090,13 +2102,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D48" t="s">
         <v>110</v>
@@ -2104,13 +2116,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>83</v>
+        <v>110</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="D49" t="s">
         <v>110</v>
@@ -2118,13 +2130,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
-      </c>
-      <c r="C50" t="s">
-        <v>77</v>
+        <v>110</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="D50" t="s">
         <v>110</v>
@@ -2132,13 +2144,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>84</v>
+        <v>110</v>
+      </c>
+      <c r="C51" t="s">
+        <v>44</v>
       </c>
       <c r="D51" t="s">
         <v>110</v>
@@ -2146,13 +2158,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>85</v>
+        <v>26</v>
+      </c>
+      <c r="C52" t="s">
+        <v>72</v>
       </c>
       <c r="D52" t="s">
         <v>110</v>
@@ -2160,13 +2172,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B53" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="D53" t="s">
         <v>110</v>
@@ -2174,36 +2186,120 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>28</v>
+      </c>
+      <c r="B54" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>86</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B55" t="s">
+        <v>76</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D55" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B56" t="s">
+        <v>77</v>
+      </c>
+      <c r="C56" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>86</v>
+      </c>
+      <c r="B57" t="s">
+        <v>78</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D57" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>86</v>
+      </c>
+      <c r="B58" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D58" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" t="s">
+        <v>80</v>
+      </c>
+      <c r="D59" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>86</v>
+      </c>
+      <c r="B60" t="s">
         <v>81</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C60" t="s">
         <v>82</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D60" t="s">
         <v>110</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B34:B40">
+  <conditionalFormatting sqref="B40:B46">
     <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C34:C35">
+  <conditionalFormatting sqref="C40:C41">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48" xr:uid="{E4614C89-2D57-4F43-852D-8A26F573FE12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C54" xr:uid="{E4614C89-2D57-4F43-852D-8A26F573FE12}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C44" xr:uid="{68E3DD76-1BFC-4333-AC73-9B3FB74E4EC0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C50" xr:uid="{68E3DD76-1BFC-4333-AC73-9B3FB74E4EC0}">
       <formula1>"All Over,Back Panel,Chest,Front Panel,Hemline,Hood,Neckline,None,Pocket,Side,Sleeve"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C43" xr:uid="{ACD72D48-D0F3-49E7-971A-18ACE6F7FB55}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C49" xr:uid="{ACD72D48-D0F3-49E7-971A-18ACE6F7FB55}">
       <formula1>"Basketball,Boxing,Cricket,Football,Running,Training/Gym,Yoga,Golf,Mountain Hiking,Surfing,Mountain Biking,Mountain Trekking,Tennis,Cycling,Sailing,Baseball,Badminton,Volleyball,NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C20" xr:uid="{1BD9BDC0-1C7A-46BA-9FF1-8D9CAB869B75}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C24" xr:uid="{1BD9BDC0-1C7A-46BA-9FF1-8D9CAB869B75}">
       <formula1>"1,2,3,4,5,6,7,8,9,10"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/Flipkart_dropdown.xlsx
+++ b/config/Flipkart_dropdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4143ED80-519E-404F-ACAB-8555D3108B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0989A7A6-BE23-41E7-AF2E-0D66463AE57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="1" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="134">
   <si>
     <t>Blue</t>
   </si>
@@ -106,9 +106,6 @@
     <t>NA</t>
   </si>
   <si>
-    <t>Final Category</t>
-  </si>
-  <si>
     <t>Fabric</t>
   </si>
   <si>
@@ -376,19 +373,76 @@
     <t>Kids Tshirts</t>
   </si>
   <si>
+    <t>Boys</t>
+  </si>
+  <si>
+    <t>Girls</t>
+  </si>
+  <si>
+    <t>60% Cotton 40% Polyester</t>
+  </si>
+  <si>
+    <t>Cotton Blend</t>
+  </si>
+  <si>
     <t>Flipkart Category</t>
   </si>
   <si>
-    <t>Boys</t>
-  </si>
-  <si>
-    <t>Girls</t>
-  </si>
-  <si>
-    <t>60% Cotton 40% Polyester</t>
-  </si>
-  <si>
-    <t>Cotton Blend</t>
+    <t>Oversized Fit</t>
+  </si>
+  <si>
+    <t>Oversized</t>
+  </si>
+  <si>
+    <t>Half Sleeves</t>
+  </si>
+  <si>
+    <t>2-4Y</t>
+  </si>
+  <si>
+    <t>4-6Y</t>
+  </si>
+  <si>
+    <t>6-8Y</t>
+  </si>
+  <si>
+    <t>8-10Y</t>
+  </si>
+  <si>
+    <t>10-12Y</t>
+  </si>
+  <si>
+    <t>12-14Y</t>
+  </si>
+  <si>
+    <t>14-16Y</t>
+  </si>
+  <si>
+    <t>16-18Y</t>
+  </si>
+  <si>
+    <t>2 - 4 Years</t>
+  </si>
+  <si>
+    <t>4 - 6 Years</t>
+  </si>
+  <si>
+    <t>6 - 8 Years</t>
+  </si>
+  <si>
+    <t>8 - 10 Years</t>
+  </si>
+  <si>
+    <t>10 - 12 Years</t>
+  </si>
+  <si>
+    <t>12 - 14 Years</t>
+  </si>
+  <si>
+    <t>14 - 16 Years</t>
+  </si>
+  <si>
+    <t>16 - 18 Years</t>
   </si>
 </sst>
 </file>
@@ -802,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FEB0F0-8794-4F72-85E1-24AFD1DB4E9B}">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.453125" bestFit="1" customWidth="1"/>
@@ -821,152 +875,152 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
         <v>45</v>
       </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
         <v>47</v>
       </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
         <v>49</v>
       </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
         <v>52</v>
       </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>53</v>
-      </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
         <v>57</v>
       </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>58</v>
-      </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
@@ -975,82 +1029,82 @@
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
@@ -1059,26 +1113,26 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -1087,343 +1141,357 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" t="s">
         <v>29</v>
       </c>
-      <c r="B22" t="s">
-        <v>30</v>
-      </c>
       <c r="C22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
+        <v>115</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>3</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>20</v>
+        <v>41</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" t="s">
-        <v>44</v>
+        <v>30</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="D41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
         <v>71</v>
       </c>
-      <c r="B42" t="s">
-        <v>27</v>
-      </c>
-      <c r="C42" t="s">
-        <v>27</v>
-      </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="C43" t="s">
+        <v>26</v>
       </c>
       <c r="D43" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations disablePrompts="1" count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C20" xr:uid="{CBFE714B-4631-4DFF-9C7B-2852269BFFB5}">
       <formula1>"1,2,3,4,5,6,7,8,9,10"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C38" xr:uid="{023D02B5-7958-4217-9FED-C7BE9A2676B9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C39" xr:uid="{023D02B5-7958-4217-9FED-C7BE9A2676B9}">
       <formula1>"Basketball,Boxing,Cricket,Football,Running,Training/Gym,Yoga,Golf,Mountain Hiking,Surfing,Mountain Biking,Mountain Trekking,Tennis,Cycling,Sailing,Baseball,Badminton,Volleyball,NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C39" xr:uid="{D41ED0CB-B689-42A0-B2E8-4F0E8D998AE0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C40" xr:uid="{D41ED0CB-B689-42A0-B2E8-4F0E8D998AE0}">
       <formula1>"All Over,Back Panel,Chest,Front Panel,Hemline,Hood,Neckline,None,Pocket,Side,Sleeve"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C43" xr:uid="{B6162B0D-49D3-4C3B-893C-A5A495DA54BF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C44" xr:uid="{B6162B0D-49D3-4C3B-893C-A5A495DA54BF}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1433,7 +1501,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B24816C5-4C62-46C4-A958-7B4B4D77D485}">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.453125" bestFit="1" customWidth="1"/>
@@ -1453,152 +1521,152 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" t="s">
         <v>45</v>
       </c>
-      <c r="B2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" t="s">
         <v>47</v>
       </c>
-      <c r="B3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
         <v>49</v>
       </c>
-      <c r="B4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
         <v>52</v>
       </c>
-      <c r="B6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C6" t="s">
-        <v>53</v>
-      </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" t="s">
         <v>57</v>
       </c>
-      <c r="B11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" t="s">
-        <v>58</v>
-      </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
@@ -1607,699 +1675,850 @@
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
+        <v>117</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" s="3">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
         <v>29</v>
       </c>
-      <c r="B28" t="s">
-        <v>26</v>
-      </c>
       <c r="C28" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" t="s">
-        <v>65</v>
+        <v>25</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" t="s">
-        <v>90</v>
+        <v>115</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="D31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="D39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B42" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s">
-        <v>2</v>
+        <v>129</v>
       </c>
       <c r="D42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B43" t="s">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="D43" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B44" t="s">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="C44" t="s">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B45" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="C45" t="s">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>0</v>
+        <v>125</v>
+      </c>
+      <c r="C46" t="s">
+        <v>133</v>
       </c>
       <c r="D46" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B47" t="s">
-        <v>41</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>42</v>
+        <v>102</v>
+      </c>
+      <c r="C47" t="s">
+        <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>42</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>42</v>
+        <v>104</v>
+      </c>
+      <c r="C48" t="s">
+        <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>20</v>
+        <v>106</v>
+      </c>
+      <c r="C49" t="s">
+        <v>107</v>
       </c>
       <c r="D49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>34</v>
+        <v>86</v>
+      </c>
+      <c r="C50" t="s">
+        <v>86</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="D51" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B54" t="s">
-        <v>110</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>83</v>
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
-      </c>
-      <c r="C56" t="s">
-        <v>77</v>
+        <v>3</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="D57" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="D58" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>80</v>
-      </c>
-      <c r="C59" t="s">
-        <v>80</v>
+        <v>109</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="B60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" t="s">
+        <v>71</v>
+      </c>
+      <c r="D62" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" t="s">
+        <v>109</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>85</v>
+      </c>
+      <c r="B65" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>85</v>
+      </c>
+      <c r="B66" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" t="s">
+        <v>76</v>
+      </c>
+      <c r="D66" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>85</v>
+      </c>
+      <c r="B67" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D67" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>85</v>
+      </c>
+      <c r="B68" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D68" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>85</v>
+      </c>
+      <c r="B69" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69" t="s">
+        <v>79</v>
+      </c>
+      <c r="D69" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70" t="s">
         <v>81</v>
       </c>
-      <c r="C60" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" t="s">
-        <v>110</v>
+      <c r="D70" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>85</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B40:B46">
+  <conditionalFormatting sqref="B50:B56">
     <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C40:C41">
+  <conditionalFormatting sqref="C50:C51">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C54" xr:uid="{E4614C89-2D57-4F43-852D-8A26F573FE12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C64" xr:uid="{E4614C89-2D57-4F43-852D-8A26F573FE12}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C50" xr:uid="{68E3DD76-1BFC-4333-AC73-9B3FB74E4EC0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C60" xr:uid="{68E3DD76-1BFC-4333-AC73-9B3FB74E4EC0}">
       <formula1>"All Over,Back Panel,Chest,Front Panel,Hemline,Hood,Neckline,None,Pocket,Side,Sleeve"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C49" xr:uid="{ACD72D48-D0F3-49E7-971A-18ACE6F7FB55}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C59" xr:uid="{ACD72D48-D0F3-49E7-971A-18ACE6F7FB55}">
       <formula1>"Basketball,Boxing,Cricket,Football,Running,Training/Gym,Yoga,Golf,Mountain Hiking,Surfing,Mountain Biking,Mountain Trekking,Tennis,Cycling,Sailing,Baseball,Badminton,Volleyball,NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C24" xr:uid="{1BD9BDC0-1C7A-46BA-9FF1-8D9CAB869B75}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C25" xr:uid="{1BD9BDC0-1C7A-46BA-9FF1-8D9CAB869B75}">
       <formula1>"1,2,3,4,5,6,7,8,9,10"</formula1>
     </dataValidation>
   </dataValidations>
